--- a/tests/perf_v2/perf_history/v2.4.2/multi_label_cls/MULTI_LABEL_CLS-raw-multilabel_medium_edsavehicle.xlsx
+++ b/tests/perf_v2/perf_history/v2.4.2/multi_label_cls/MULTI_LABEL_CLS-raw-multilabel_medium_edsavehicle.xlsx
@@ -583,53 +583,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="C2" t="n">
-        <v>118.0073654651642</v>
+        <v>210.943051815033</v>
       </c>
       <c r="D2" t="n">
-        <v>1.669999957084656</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8684848546981812</v>
+        <v>0.8993939161300659</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8463636636734009</v>
+        <v>0.8672727346420288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8513636589050293</v>
+        <v>0.8659090995788574</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8463636636734009</v>
+        <v>0.864545464515686</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0935467050611217</v>
+        <v>0.0783266349288517</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1372438073158264</v>
+        <v>0.1323749274015426</v>
       </c>
       <c r="K2" t="n">
-        <v>24.21196365356445</v>
+        <v>22.99541211128235</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0124070477485656</v>
+        <v>0.009991930723190301</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0183383929729461</v>
+        <v>0.0187508225440979</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0253752040863037</v>
+        <v>0.0233460879325866</v>
       </c>
       <c r="O2" t="n">
-        <v>3.667678594589233</v>
+        <v>3.75016450881958</v>
       </c>
       <c r="P2" t="n">
-        <v>5.075040817260742</v>
+        <v>4.669217586517334</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-130239</t>
+          <t>20250714-173054</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -674,13 +674,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -690,7 +692,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -699,53 +701,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="C3" t="n">
-        <v>197.6054294109344</v>
+        <v>101.3099658489227</v>
       </c>
       <c r="D3" t="n">
-        <v>1.710000038146973</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8903030157089233</v>
+        <v>0.875151515007019</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8613636493682861</v>
+        <v>0.8550000190734863</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8590909242630005</v>
+        <v>0.8545454740524292</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8627272844314575</v>
+        <v>0.8454545736312866</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0957891272224542</v>
+        <v>0.07869844204640079</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1249311044812202</v>
+        <v>0.0793184861540794</v>
       </c>
       <c r="K3" t="n">
-        <v>23.94837236404419</v>
+        <v>22.4688708782196</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0104918658733367</v>
+        <v>0.0107070839405059</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0196599602699279</v>
+        <v>0.0184384179115295</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0240596270561218</v>
+        <v>0.0253910768032074</v>
       </c>
       <c r="O3" t="n">
-        <v>3.931992053985596</v>
+        <v>3.687683582305908</v>
       </c>
       <c r="P3" t="n">
-        <v>4.811925411224365</v>
+        <v>5.07821536064148</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-130553</t>
+          <t>20250714-173523</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -790,13 +792,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -806,7 +810,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -815,53 +819,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C4" t="n">
-        <v>197.5923938751221</v>
+        <v>125.524284362793</v>
       </c>
       <c r="D4" t="n">
-        <v>1.690000057220459</v>
+        <v>1.759999990463257</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8824242353439331</v>
+        <v>0.8769696950912476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8586363792419434</v>
+        <v>0.8590909242630005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8604545593261719</v>
+        <v>0.8568181991577148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8586363792419434</v>
+        <v>0.8563636541366577</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0959200192498796</v>
+        <v>0.0778582339937036</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0890721976757049</v>
+        <v>0.086971990764141</v>
       </c>
       <c r="K4" t="n">
-        <v>24.50327348709106</v>
+        <v>23.10596227645874</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0101406419277191</v>
+        <v>0.0094438469409942</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0191916692256927</v>
+        <v>0.0187417066097259</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0233618783950805</v>
+        <v>0.0236356472969055</v>
       </c>
       <c r="O4" t="n">
-        <v>3.83833384513855</v>
+        <v>3.74834132194519</v>
       </c>
       <c r="P4" t="n">
-        <v>4.672375679016113</v>
+        <v>4.727129459381104</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-131026</t>
+          <t>20250714-173802</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -906,13 +910,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -922,7 +928,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -931,53 +937,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>185.637957572937</v>
+        <v>85.63587832450867</v>
       </c>
       <c r="D5" t="n">
-        <v>1.620000004768372</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8921211957931519</v>
+        <v>0.8684848546981812</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8622727394104004</v>
+        <v>0.8554545640945435</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8627272844314575</v>
+        <v>0.8563636541366577</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8586363792419434</v>
+        <v>0.8509091138839722</v>
       </c>
       <c r="I5" t="n">
-        <v>0.095881995025689</v>
+        <v>0.0773719268948284</v>
       </c>
       <c r="J5" t="n">
-        <v>0.078298769891262</v>
+        <v>0.1256170719861984</v>
       </c>
       <c r="K5" t="n">
-        <v>25.60058259963989</v>
+        <v>22.53442740440369</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0100200724601745</v>
+        <v>0.0097214758396148</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0206853652000427</v>
+        <v>0.0188166010379791</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0241950094699859</v>
+        <v>0.0237602138519287</v>
       </c>
       <c r="O5" t="n">
-        <v>4.137073040008545</v>
+        <v>3.763320207595825</v>
       </c>
       <c r="P5" t="n">
-        <v>4.839001893997192</v>
+        <v>4.752042770385742</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-131500</t>
+          <t>20250714-174106</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1022,13 +1028,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1038,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1047,53 +1055,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="C6" t="n">
-        <v>138.2320640087128</v>
+        <v>161.3746316432953</v>
       </c>
       <c r="D6" t="n">
         <v>1.690000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8721212148666382</v>
+        <v>0.8787878751754761</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8568181991577148</v>
+        <v>0.8581818342208862</v>
       </c>
       <c r="G6" t="n">
+        <v>0.8581818342208862</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.8586363792419434</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.860909104347229</v>
-      </c>
       <c r="I6" t="n">
-        <v>0.0957744131376454</v>
+        <v>0.0791482419714214</v>
       </c>
       <c r="J6" t="n">
-        <v>0.122457206249237</v>
+        <v>0.1279702186584472</v>
       </c>
       <c r="K6" t="n">
-        <v>26.78741717338562</v>
+        <v>22.61975121498108</v>
       </c>
       <c r="L6" t="n">
-        <v>0.010511370897293</v>
+        <v>0.0098552167415618</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0216967451572418</v>
+        <v>0.0207727205753326</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0238698709011077</v>
+        <v>0.0241554510593414</v>
       </c>
       <c r="O6" t="n">
-        <v>4.339349031448364</v>
+        <v>4.154544115066528</v>
       </c>
       <c r="P6" t="n">
-        <v>4.773974180221558</v>
+        <v>4.831090211868286</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-131924</t>
+          <t>20250714-174329</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1138,13 +1146,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1154,7 +1164,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1324,53 +1334,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>187.2011394500732</v>
+        <v>118.2462363243103</v>
       </c>
       <c r="D2" t="n">
-        <v>4.320000171661377</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8915151357650757</v>
+        <v>0.8921211957931519</v>
       </c>
       <c r="F2" t="n">
-        <v>0.871363639831543</v>
+        <v>0.8586363792419434</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8695454597473145</v>
+        <v>0.860909104347229</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8740909099578857</v>
+        <v>0.8636363744735718</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1032693451192198</v>
+        <v>0.0881729056609087</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0954720750451088</v>
+        <v>0.0976944267749786</v>
       </c>
       <c r="K2" t="n">
-        <v>18.88723516464233</v>
+        <v>17.52246809005737</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0094210660457611</v>
+        <v>0.0077387309074401</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0203238880634307</v>
+        <v>0.0173121774196624</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0213595938682556</v>
+        <v>0.0207202696800231</v>
       </c>
       <c r="O2" t="n">
-        <v>4.064777612686157</v>
+        <v>3.462435483932495</v>
       </c>
       <c r="P2" t="n">
-        <v>4.271918773651123</v>
+        <v>4.144053936004639</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-102229</t>
+          <t>20250714-150847</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1415,13 +1425,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1431,7 +1443,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1440,53 +1452,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
-        <v>150.4230432510376</v>
+        <v>71.29900646209717</v>
       </c>
       <c r="D3" t="n">
         <v>4.320000171661377</v>
       </c>
       <c r="E3" t="n">
-        <v>0.892727255821228</v>
+        <v>0.8624242544174194</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8663636445999146</v>
+        <v>0.8445454835891724</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8654545545578003</v>
+        <v>0.8440909385681152</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8631818294525146</v>
+        <v>0.8490909337997437</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1025521445431207</v>
+        <v>0.0870553325204288</v>
       </c>
       <c r="J3" t="n">
-        <v>0.098085306584835</v>
+        <v>0.0888698697090148</v>
       </c>
       <c r="K3" t="n">
-        <v>19.35991954803467</v>
+        <v>17.6061589717865</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0105442607402801</v>
+        <v>0.007916260957717801</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0189038276672363</v>
+        <v>0.0169871985912323</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0217327940464019</v>
+        <v>0.0230216419696807</v>
       </c>
       <c r="O3" t="n">
-        <v>3.780765533447266</v>
+        <v>3.39743971824646</v>
       </c>
       <c r="P3" t="n">
-        <v>4.346558809280396</v>
+        <v>4.604328393936157</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-102631</t>
+          <t>20250714-151135</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1531,13 +1543,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1547,7 +1561,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1556,53 +1570,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>177.5737457275391</v>
+        <v>96.77976417541504</v>
       </c>
       <c r="D4" t="n">
         <v>4.320000171661377</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8921211957931519</v>
+        <v>0.8848484754562378</v>
       </c>
       <c r="F4" t="n">
+        <v>0.8627272844314575</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8640909194946289</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.8709090948104858</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.8740909099578857</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8722727298736572</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.1014777175110319</v>
+        <v>0.0877071844649986</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1374716311693191</v>
+        <v>0.09290432184934611</v>
       </c>
       <c r="K4" t="n">
-        <v>19.25272369384766</v>
+        <v>18.08964204788208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0092687487602233</v>
+        <v>0.0083049690723419</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0175212621688842</v>
+        <v>0.0177277779579162</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0235582160949707</v>
+        <v>0.0201062822341918</v>
       </c>
       <c r="O4" t="n">
-        <v>3.504252433776855</v>
+        <v>3.545555591583252</v>
       </c>
       <c r="P4" t="n">
-        <v>4.711643218994141</v>
+        <v>4.021256446838379</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-102957</t>
+          <t>20250714-151336</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1647,13 +1661,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1663,7 +1679,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1672,53 +1688,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>149.0031969547272</v>
+        <v>112.5133454799652</v>
       </c>
       <c r="D5" t="n">
-        <v>4.389999866485596</v>
+        <v>4.360000133514404</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8872727155685425</v>
+        <v>0.8896969556808472</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8686363697052002</v>
+        <v>0.8650000095367432</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8709090948104858</v>
+        <v>0.8668181896209717</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8650000095367432</v>
+        <v>0.8672727346420288</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1030827216411891</v>
+        <v>0.0876821564084075</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1274870038032531</v>
+        <v>0.0944196879863739</v>
       </c>
       <c r="K5" t="n">
-        <v>19.50889492034912</v>
+        <v>17.46692967414856</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0095181441307067</v>
+        <v>0.0074932789802551</v>
       </c>
       <c r="M5" t="n">
-        <v>0.017659432888031</v>
+        <v>0.0177518510818481</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0215913009643554</v>
+        <v>0.0222633564472198</v>
       </c>
       <c r="O5" t="n">
-        <v>3.531886577606201</v>
+        <v>3.550370216369629</v>
       </c>
       <c r="P5" t="n">
-        <v>4.318260192871094</v>
+        <v>4.45267128944397</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-103350</t>
+          <t>20250714-151603</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1763,13 +1779,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1779,7 +1797,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1788,53 +1806,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C6" t="n">
-        <v>125.1439871788025</v>
+        <v>144.5635824203491</v>
       </c>
       <c r="D6" t="n">
-        <v>4.300000190734863</v>
+        <v>4.360000133514404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8915151357650757</v>
+        <v>0.8969696760177612</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8695454597473145</v>
+        <v>0.8668181896209717</v>
       </c>
       <c r="G6" t="n">
         <v>0.8704545497894287</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8668181896209717</v>
+        <v>0.871363639831543</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1041960443688344</v>
+        <v>0.08766012102644009</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1288229525089264</v>
+        <v>0.08096055686473839</v>
       </c>
       <c r="K6" t="n">
-        <v>19.20955157279968</v>
+        <v>18.23520469665528</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0099274039268493</v>
+        <v>0.0077576339244842</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0167449140548706</v>
+        <v>0.0172777450084686</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0238906157016754</v>
+        <v>0.0206016945838928</v>
       </c>
       <c r="O6" t="n">
-        <v>3.348982810974121</v>
+        <v>3.455549001693726</v>
       </c>
       <c r="P6" t="n">
-        <v>4.778123140335083</v>
+        <v>4.120338916778564</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-103716</t>
+          <t>20250714-151846</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1879,13 +1897,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1895,7 +1915,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2065,53 +2085,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>253.9678416252136</v>
+        <v>202.2485897541046</v>
       </c>
       <c r="D2" t="n">
         <v>5.699999809265137</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9024242162704468</v>
+        <v>0.8957575559616089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8827272653579712</v>
+        <v>0.8795454502105713</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8795454502105713</v>
+        <v>0.8818181753158569</v>
       </c>
       <c r="H2" t="n">
         <v>0.8804545402526855</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1366463396844901</v>
+        <v>0.1200863573214281</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1090816110372543</v>
+        <v>0.1108494400978088</v>
       </c>
       <c r="K2" t="n">
-        <v>47.32951235771179</v>
+        <v>39.75031971931458</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0163555347919464</v>
+        <v>0.0187512266635894</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0244947242736816</v>
+        <v>0.0236950957775115</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0320623207092285</v>
+        <v>0.030368640422821</v>
       </c>
       <c r="O2" t="n">
-        <v>4.898944854736328</v>
+        <v>4.739019155502319</v>
       </c>
       <c r="P2" t="n">
-        <v>6.412464141845703</v>
+        <v>6.073728084564209</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-112013</t>
+          <t>20250714-160033</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2156,13 +2176,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2172,7 +2194,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2184,50 +2206,50 @@
         <v>95</v>
       </c>
       <c r="C3" t="n">
-        <v>193.057834148407</v>
+        <v>170.4320862293243</v>
       </c>
       <c r="D3" t="n">
-        <v>5.699999809265137</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8987878561019897</v>
+        <v>0.9012120962142944</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8772727251052856</v>
+        <v>0.871363639831543</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8813636302947998</v>
+        <v>0.8736363649368286</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8849999904632568</v>
+        <v>0.8836363554000854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1373798198605838</v>
+        <v>0.1201522875773278</v>
       </c>
       <c r="J3" t="n">
-        <v>0.125174194574356</v>
+        <v>0.1175227835774421</v>
       </c>
       <c r="K3" t="n">
-        <v>46.27129602432251</v>
+        <v>40.69754910469055</v>
       </c>
       <c r="L3" t="n">
-        <v>0.017950450181961</v>
+        <v>0.0200478196144104</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0235656094551086</v>
+        <v>0.0236778485774993</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0330559110641479</v>
+        <v>0.0308077883720397</v>
       </c>
       <c r="O3" t="n">
-        <v>4.713121891021729</v>
+        <v>4.735569715499878</v>
       </c>
       <c r="P3" t="n">
-        <v>6.61118221282959</v>
+        <v>6.161557674407959</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-112606</t>
+          <t>20250714-160529</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2272,13 +2294,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2288,7 +2312,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2297,53 +2321,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C4" t="n">
-        <v>168.1876139640808</v>
+        <v>162.270200252533</v>
       </c>
       <c r="D4" t="n">
         <v>5.699999809265137</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8969696760177612</v>
+        <v>0.9006060361862183</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8745454549789429</v>
+        <v>0.8781818151473999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8731818199157715</v>
+        <v>0.8781818151473999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.875</v>
+        <v>0.8736363649368286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1363239446318293</v>
+        <v>0.1197237240580411</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1150902658700943</v>
+        <v>0.1256065666675567</v>
       </c>
       <c r="K4" t="n">
-        <v>45.56440210342407</v>
+        <v>39.94328689575195</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0157947778701782</v>
+        <v>0.018155870437622</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0254791927337646</v>
+        <v>0.0235559487342834</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0316260039806366</v>
+        <v>0.031142394542694</v>
       </c>
       <c r="O4" t="n">
-        <v>5.09583854675293</v>
+        <v>4.711189746856689</v>
       </c>
       <c r="P4" t="n">
-        <v>6.325200796127319</v>
+        <v>6.228478908538818</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-113059</t>
+          <t>20250714-160956</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2388,13 +2412,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2404,7 +2430,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2413,53 +2439,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C5" t="n">
-        <v>137.7430896759033</v>
+        <v>155.0051398277283</v>
       </c>
       <c r="D5" t="n">
-        <v>5.670000076293945</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8909090757369995</v>
+        <v>0.8987878561019897</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8722727298736572</v>
+        <v>0.878636360168457</v>
       </c>
       <c r="G5" t="n">
-        <v>0.871363639831543</v>
+        <v>0.8795454502105713</v>
       </c>
       <c r="H5" t="n">
         <v>0.878636360168457</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1359082232437916</v>
+        <v>0.1203357653542496</v>
       </c>
       <c r="J5" t="n">
-        <v>0.140581876039505</v>
+        <v>0.1065529808402061</v>
       </c>
       <c r="K5" t="n">
-        <v>45.88225555419922</v>
+        <v>40.04045224189758</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0159274780750274</v>
+        <v>0.0195185434818267</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0234535944461822</v>
+        <v>0.0233543634414672</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0316887879371643</v>
+        <v>0.0302217328548431</v>
       </c>
       <c r="O5" t="n">
-        <v>4.69071888923645</v>
+        <v>4.670872688293457</v>
       </c>
       <c r="P5" t="n">
-        <v>6.337757587432861</v>
+        <v>6.044346570968628</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-113525</t>
+          <t>20250714-161412</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2504,13 +2530,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2520,7 +2548,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2529,53 +2557,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C6" t="n">
-        <v>129.4020326137543</v>
+        <v>141.6269180774689</v>
       </c>
       <c r="D6" t="n">
-        <v>5.699999809265137</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8963636159896851</v>
+        <v>0.9042423963546752</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8768181800842285</v>
+        <v>0.8795454502105713</v>
       </c>
       <c r="G6" t="n">
+        <v>0.878636360168457</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.8781818151473999</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.8772727251052856</v>
-      </c>
       <c r="I6" t="n">
-        <v>0.1371968315234259</v>
+        <v>0.1196719640040699</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1296052783727646</v>
+        <v>0.1108592599630355</v>
       </c>
       <c r="K6" t="n">
-        <v>45.54115557670593</v>
+        <v>40.00413751602173</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0159345340728759</v>
+        <v>0.0178180158138275</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0234554278850555</v>
+        <v>0.0243386733531951</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0295681536197662</v>
+        <v>0.0290265572071075</v>
       </c>
       <c r="O6" t="n">
-        <v>4.691085577011108</v>
+        <v>4.867734670639038</v>
       </c>
       <c r="P6" t="n">
-        <v>5.913630723953247</v>
+        <v>5.805311441421509</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-113921</t>
+          <t>20250714-161821</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -2620,13 +2648,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2636,7 +2666,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2806,53 +2836,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C2" t="n">
-        <v>188.9047288894653</v>
+        <v>149.3952176570892</v>
       </c>
       <c r="D2" t="n">
-        <v>2.440000057220459</v>
+        <v>2.450000047683716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8933333158493042</v>
+        <v>0.8915151357650757</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8736363649368286</v>
+        <v>0.8759090900421143</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8768181800842285</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8777272701263428</v>
+        <v>0.8677272796630859</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0953699755152379</v>
+        <v>0.078452733259241</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1117738038301467</v>
+        <v>0.0935384184122085</v>
       </c>
       <c r="K2" t="n">
-        <v>17.57733988761902</v>
+        <v>15.88595962524414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008362425565719599</v>
+        <v>0.0074452376365661</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0171725380420684</v>
+        <v>0.0180928421020507</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0215050828456878</v>
+        <v>0.0213437259197235</v>
       </c>
       <c r="O2" t="n">
-        <v>3.434507608413696</v>
+        <v>3.618568420410156</v>
       </c>
       <c r="P2" t="n">
-        <v>4.301016569137573</v>
+        <v>4.268745183944702</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-121638</t>
+          <t>20250714-165313</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2897,13 +2927,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2913,7 +2945,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2922,53 +2954,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C3" t="n">
-        <v>78.61675906181335</v>
+        <v>95.83893251419067</v>
       </c>
       <c r="D3" t="n">
-        <v>2.569999933242798</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.867878794670105</v>
+        <v>0.8878787755966187</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8622727394104004</v>
+        <v>0.8590909242630005</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8618181943893433</v>
+        <v>0.8554545640945435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.857272744178772</v>
+        <v>0.8631818294525146</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0964665979731316</v>
+        <v>0.07825448155403129</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1136927902698516</v>
+        <v>0.0382667072117328</v>
       </c>
       <c r="K3" t="n">
-        <v>17.21323347091675</v>
+        <v>15.77431201934814</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0094810926914215</v>
+        <v>0.0098641490936279</v>
       </c>
       <c r="M3" t="n">
-        <v>0.017776391506195</v>
+        <v>0.0164263403415679</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0207213497161865</v>
+        <v>0.0200445568561553</v>
       </c>
       <c r="O3" t="n">
-        <v>3.555278301239014</v>
+        <v>3.285268068313598</v>
       </c>
       <c r="P3" t="n">
-        <v>4.144269943237305</v>
+        <v>4.008911371231079</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-122040</t>
+          <t>20250714-165629</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -3013,13 +3045,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -3029,7 +3063,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3038,53 +3072,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C4" t="n">
-        <v>112.8127880096436</v>
+        <v>115.366592168808</v>
       </c>
       <c r="D4" t="n">
-        <v>2.400000095367432</v>
+        <v>2.450000047683716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8921211957931519</v>
+        <v>0.8909090757369995</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8650000095367432</v>
+        <v>0.8636363744735718</v>
       </c>
       <c r="G4" t="n">
         <v>0.8627272844314575</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8618181943893433</v>
+        <v>0.8681818246841431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0954998771349588</v>
+        <v>0.0773037208633108</v>
       </c>
       <c r="J4" t="n">
-        <v>0.050529945641756</v>
+        <v>0.1076707765460014</v>
       </c>
       <c r="K4" t="n">
-        <v>18.07761001586914</v>
+        <v>16.07820630073547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0107671201229095</v>
+        <v>0.0074993872642517</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0174191176891326</v>
+        <v>0.0167681789398193</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0225278615951538</v>
+        <v>0.0202557361125946</v>
       </c>
       <c r="O4" t="n">
-        <v>3.483823537826538</v>
+        <v>3.353635787963867</v>
       </c>
       <c r="P4" t="n">
-        <v>4.505572319030762</v>
+        <v>4.051147222518921</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-122250</t>
+          <t>20250714-165852</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -3129,13 +3163,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -3145,7 +3181,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3154,53 +3190,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>181.9017872810364</v>
+        <v>95.54610800743104</v>
       </c>
       <c r="D5" t="n">
-        <v>2.440000057220459</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8909090757369995</v>
+        <v>0.8830302953720093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8709090948104858</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8709090948104858</v>
+        <v>0.8704545497894287</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8763636350631714</v>
+        <v>0.8695454597473145</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0939825189913191</v>
+        <v>0.07750439067681621</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1192346066236496</v>
+        <v>0.1119160056114196</v>
       </c>
       <c r="K5" t="n">
-        <v>16.89439964294434</v>
+        <v>15.55423331260681</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0088518786430358</v>
+        <v>0.0076141643524169</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0177347946166992</v>
+        <v>0.0162814617156982</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0208196365833282</v>
+        <v>0.0212512052059173</v>
       </c>
       <c r="O5" t="n">
-        <v>3.546958923339844</v>
+        <v>3.256292343139648</v>
       </c>
       <c r="P5" t="n">
-        <v>4.163927316665649</v>
+        <v>4.250241041183472</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-122537</t>
+          <t>20250714-170134</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -3245,13 +3281,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -3261,7 +3299,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3270,53 +3308,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="C6" t="n">
-        <v>183.9882392883301</v>
+        <v>67.06690621376038</v>
       </c>
       <c r="D6" t="n">
-        <v>2.490000009536743</v>
+        <v>2.420000076293945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8963636159896851</v>
+        <v>0.8690909147262573</v>
       </c>
       <c r="F6" t="n">
-        <v>0.875</v>
+        <v>0.8568181991577148</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8740909099578857</v>
+        <v>0.8581818342208862</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8754545450210571</v>
+        <v>0.8545454740524292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0970564715988267</v>
+        <v>0.0799451195726207</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1290449202060699</v>
+        <v>0.0806748494505882</v>
       </c>
       <c r="K6" t="n">
-        <v>17.52194237709045</v>
+        <v>16.15453290939331</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0086590504646301</v>
+        <v>0.0076823794841766</v>
       </c>
       <c r="M6" t="n">
-        <v>0.019341834783554</v>
+        <v>0.0181895327568054</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0209818804264068</v>
+        <v>0.0197888195514678</v>
       </c>
       <c r="O6" t="n">
-        <v>3.868366956710816</v>
+        <v>3.637906551361084</v>
       </c>
       <c r="P6" t="n">
-        <v>4.196376085281372</v>
+        <v>3.957763910293579</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-122930</t>
+          <t>20250714-170356</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3361,13 +3399,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -3377,7 +3417,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
